--- a/雲端試算表副本/天泰工區車輛名冊_最新副本.xlsx
+++ b/雲端試算表副本/天泰工區車輛名冊_最新副本.xlsx
@@ -683,15 +683,48 @@
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" t="str">
+        <v>陳皇龍</v>
+      </c>
+      <c r="D18" t="str">
+        <v>量子輻射</v>
+      </c>
+      <c r="F18" t="str">
+        <v>副總</v>
+      </c>
+      <c r="H18" t="str">
+        <v>RFV-2826</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
+      <c r="D19" t="str">
+        <v>量子輻射</v>
+      </c>
+      <c r="F19" t="str">
+        <v>副總</v>
+      </c>
+      <c r="H19" t="str">
+        <v>RFY-7266</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
         <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>徐技師</v>
+      </c>
+      <c r="D20" t="str">
+        <v>汙水廠商</v>
+      </c>
+      <c r="F20" t="str">
+        <v>技師</v>
+      </c>
+      <c r="H20" t="str">
+        <v>BQY-7008</v>
       </c>
     </row>
     <row r="21">
